--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>ABAD</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
   </si>
   <si>
     <t>MARITZA</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
   </si>
   <si>
     <t>ANGELA MONTSERRAT</t>
@@ -618,16 +612,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>26</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.3</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -641,16 +638,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H3">
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -664,16 +664,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>18</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -738,7 +741,7 @@
         <v>96.3</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,16 +758,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,16 +784,16 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -838,10 +841,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -850,21 +853,21 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330050470596</v>
+        <v>20330051920383</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -873,29 +876,6 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920383</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -803,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -835,25 +841,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>20330051920356</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -864,10 +870,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -876,6 +882,29 @@
         <v>13</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920331</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,28 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>PONCE</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
     <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
   </si>
 </sst>
 </file>
@@ -809,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,16 +835,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920356</v>
+        <v>20330051920383</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -864,47 +858,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920383</v>
+        <v>21330051920331</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920331</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -79,19 +79,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ABAD</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
   </si>
   <si>
     <t>MARITZA</t>
@@ -495,10 +486,10 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -507,7 +498,7 @@
         <v>96.3</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,10 +512,10 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>11</v>
@@ -533,7 +524,7 @@
         <v>73.33</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,10 +538,10 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -559,7 +550,7 @@
         <v>76.19</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -612,10 +603,10 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -624,7 +615,7 @@
         <v>96.3</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -638,19 +629,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -664,19 +655,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -729,10 +720,10 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -741,7 +732,7 @@
         <v>96.3</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,19 +746,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,19 +772,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -835,47 +826,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920383</v>
+        <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920331</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
   </si>
 </sst>
 </file>
@@ -723,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -749,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,7 +775,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -794,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -824,29 +815,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20221.xlsx
@@ -775,7 +775,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
